--- a/src/analyses/linear_regression/AffliationTo.xlsx
+++ b/src/analyses/linear_regression/AffliationTo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,16 +477,16 @@
         <v>45195</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Channel.C_005</t>
+          <t>Channel.C_011_Unit 1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(650.0, 800.0)</t>
+          <t>(700.0, 1000.0)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,11 +496,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7785653368373999</v>
+        <v>0.6451536097075046</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +511,16 @@
         <v>45195</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Channel.C_005</t>
+          <t>Channel.C_011_Unit 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(650.0, 800.0)</t>
+          <t>(700.0, 1000.0)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -530,11 +530,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.2620962788225971</v>
+        <v>0.5249129683966012</v>
       </c>
     </row>
     <row r="4">
@@ -545,16 +545,16 @@
         <v>45195</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Channel.C_005</t>
+          <t>Channel.C_011_Unit 1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(650.0, 800.0)</t>
+          <t>(700.0, 1000.0)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -564,11 +564,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7784774966386546</v>
+        <v>0.7991929244806958</v>
       </c>
     </row>
     <row r="5">
@@ -579,16 +579,16 @@
         <v>45195</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Channel.C_025</t>
+          <t>Channel.C_011_Unit 1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(650.0, 800.0)</t>
+          <t>(700.0, 1000.0)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -598,11 +598,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8384613373845479</v>
+        <v>0.268061492879328</v>
       </c>
     </row>
     <row r="6">
@@ -613,16 +613,16 @@
         <v>45195</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Channel.C_025</t>
+          <t>Channel.C_020</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(650.0, 800.0)</t>
+          <t>(50.0, 150.0)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -632,11 +632,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.6039811256471974</v>
+        <v>0.30432191038059</v>
       </c>
     </row>
     <row r="7">
@@ -647,16 +647,16 @@
         <v>45195</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_027_Unit 2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(100.0, 250.0)</t>
+          <t>(150.0, 350.0)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -666,11 +666,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3442206689121549</v>
+        <v>0.3832754583321659</v>
       </c>
     </row>
     <row r="8">
@@ -681,16 +681,16 @@
         <v>45195</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_027_Unit 2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(650.0, 800.0)</t>
+          <t>(150.0, 350.0)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -700,11 +700,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.9340384695984407</v>
+        <v>0.278620222251573</v>
       </c>
     </row>
     <row r="9">
@@ -715,16 +715,16 @@
         <v>45195</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(650.0, 800.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -734,11 +734,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.633456198353475</v>
+        <v>0.3491276898742337</v>
       </c>
     </row>
     <row r="10">
@@ -746,19 +746,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Channel.C_027</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(650.0, 800.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -768,11 +768,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.6187305757277084</v>
+        <v>0.3125039577001013</v>
       </c>
     </row>
     <row r="11">
@@ -780,19 +780,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(0.0, 300.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -802,11 +802,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.5092734647876507</v>
+        <v>0.6843039094368638</v>
       </c>
     </row>
     <row r="12">
@@ -814,19 +814,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45195</v>
+        <v>45202</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(200.0, 400.0)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -836,11 +836,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.30432191038059</v>
+        <v>0.4105341754631779</v>
       </c>
     </row>
     <row r="13">
@@ -851,16 +851,16 @@
         <v>45202</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Channel.C_010</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(300.0, 400.0)</t>
+          <t>(2150.0, 2250.0)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -870,11 +870,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.6800920178437024</v>
+        <v>0.3937074669949256</v>
       </c>
     </row>
     <row r="14">
@@ -885,16 +885,16 @@
         <v>45202</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Channel.C_010</t>
+          <t>Channel.C_006_Unit 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(300.0, 400.0)</t>
+          <t>(2150.0, 2250.0)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,11 +904,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.4780528131109093</v>
+        <v>0.7370731861442186</v>
       </c>
     </row>
     <row r="15">
@@ -919,16 +919,16 @@
         <v>45202</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Channel.C_010_Unit 2</t>
+          <t>Channel.C_026_Unit 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(200.0, 600.0)</t>
+          <t>(1900.0, 2000.0)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.4950756104970486</v>
+        <v>0.2563276338488107</v>
       </c>
     </row>
     <row r="16">
@@ -953,11 +953,11 @@
         <v>45202</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Channel.C_010_Unit 2</t>
+          <t>Channel.C_013_Unit 1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -972,11 +972,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.4497544497197339</v>
+        <v>0.2946290782193175</v>
       </c>
     </row>
     <row r="17">
@@ -987,11 +987,11 @@
         <v>45202</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Channel.C_010_Unit 2</t>
+          <t>Channel.C_013_Unit 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1006,11 +1006,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.4902751137235091</v>
+        <v>0.3890611754606188</v>
       </c>
     </row>
     <row r="18">
@@ -1018,19 +1018,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_013_Unit 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(500.0, 600.0)</t>
+          <t>(200.0, 600.0)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1040,11 +1040,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.5025351047246737</v>
+        <v>0.7679440243156804</v>
       </c>
     </row>
     <row r="19">
@@ -1052,19 +1052,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_013_Unit 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(500.0, 600.0)</t>
+          <t>(200.0, 600.0)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1074,11 +1074,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.5070831340119798</v>
+        <v>0.4791021024572061</v>
       </c>
     </row>
     <row r="20">
@@ -1086,19 +1086,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Channel.C_022</t>
+          <t>Channel.C_006</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(350.0, 500.0)</t>
+          <t>(450.0, 650.0)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1108,11 +1108,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.8126041760021911</v>
+        <v>0.2522887548210729</v>
       </c>
     </row>
     <row r="21">
@@ -1120,19 +1120,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Channel.C_022</t>
+          <t>Channel.C_006</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(350.0, 500.0)</t>
+          <t>(450.0, 650.0)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1142,11 +1142,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.4551247174377382</v>
+        <v>0.301740845284409</v>
       </c>
     </row>
     <row r="22">
@@ -1154,19 +1154,19 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Channel.C_022</t>
+          <t>Channel.C_006</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(350.0, 500.0)</t>
+          <t>(450.0, 650.0)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.2562044957759521</v>
+        <v>0.3188814020171484</v>
       </c>
     </row>
     <row r="23">
@@ -1188,19 +1188,19 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Channel.C_009</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(1550.0, 1650.0)</t>
+          <t>(200.0, 650.0)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1210,11 +1210,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.4418526689707171</v>
+        <v>0.4700854591466959</v>
       </c>
     </row>
     <row r="24">
@@ -1222,19 +1222,19 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Channel.C_009</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(1550.0, 1650.0)</t>
+          <t>(200.0, 650.0)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.8687559191892908</v>
+        <v>0.4715179610566315</v>
       </c>
     </row>
     <row r="25">
@@ -1256,19 +1256,19 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Channel.C_009</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(1550.0, 1650.0)</t>
+          <t>(200.0, 650.0)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.5527154346616233</v>
+        <v>0.508597460396423</v>
       </c>
     </row>
     <row r="26">
@@ -1290,19 +1290,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Channel.C_009</t>
+          <t>Channel.C_026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(1550.0, 1650.0)</t>
+          <t>(1000.0, 1100.0)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1312,11 +1312,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.286073121707961</v>
+        <v>0.5784171361449992</v>
       </c>
     </row>
     <row r="27">
@@ -1324,19 +1324,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45210</v>
+        <v>45202</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(1050.0, 1150.0)</t>
+          <t>(1000.0, 1100.0)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.3162011481898098</v>
+        <v>0.2623367080212539</v>
       </c>
     </row>
     <row r="28">
@@ -1358,19 +1358,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45210</v>
+        <v>45202</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Channel.C_022</t>
+          <t>Channel.C_026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(1950.0, 2050.0)</t>
+          <t>(1000.0, 1100.0)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1380,11 +1380,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.3194815020220372</v>
+        <v>0.8719550890268719</v>
       </c>
     </row>
     <row r="29">
@@ -1392,19 +1392,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45210</v>
+        <v>45202</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Channel.C_022</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(1950.0, 2050.0)</t>
+          <t>(200.0, 600.0)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.2889702626918536</v>
+        <v>0.4950756104970486</v>
       </c>
     </row>
     <row r="30">
@@ -1426,19 +1426,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45210</v>
+        <v>45202</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(200.0, 600.0)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1448,11 +1448,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.759144027018426</v>
+        <v>0.4497544497197339</v>
       </c>
     </row>
     <row r="31">
@@ -1460,19 +1460,19 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45210</v>
+        <v>45202</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_010_Unit 2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(200.0, 600.0)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1482,11 +1482,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.2619753014117013</v>
+        <v>0.4902751137235091</v>
       </c>
     </row>
     <row r="32">
@@ -1494,19 +1494,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Channel.C_013</t>
+          <t>Channel.C_019_Unit 3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(1600.0, 1700.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1516,11 +1516,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.4153904837251357</v>
+        <v>0.3399959524803975</v>
       </c>
     </row>
     <row r="33">
@@ -1528,19 +1528,19 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Channel.C_013</t>
+          <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(1600.0, 1700.0)</t>
+          <t>(100.0, 700.0)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1550,11 +1550,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.3381521529430138</v>
+        <v>0.3930257378820238</v>
       </c>
     </row>
     <row r="34">
@@ -1562,19 +1562,19 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_019_Unit 3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(200.0, 650.0)</t>
+          <t>(100.0, 500.0)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1584,11 +1584,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.3324959790162958</v>
+        <v>0.3641188286886875</v>
       </c>
     </row>
     <row r="35">
@@ -1596,19 +1596,19 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_018_Unit 1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(200.0, 650.0)</t>
+          <t>(150.0, 500.0)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1618,11 +1618,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.4054620972266729</v>
+        <v>0.2826505655762765</v>
       </c>
     </row>
     <row r="36">
@@ -1630,19 +1630,19 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(200.0, 550.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1652,11 +1652,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.3885800424570278</v>
+        <v>0.2703884991498081</v>
       </c>
     </row>
     <row r="37">
@@ -1664,19 +1664,19 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_004_Unit 2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(200.0, 550.0)</t>
+          <t>(100.0, 500.0)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.3609523936437014</v>
+        <v>0.6400862798135454</v>
       </c>
     </row>
     <row r="38">
@@ -1698,19 +1698,19 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(200.0, 550.0)</t>
+          <t>(150.0, 500.0)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1720,11 +1720,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.2698376884643598</v>
+        <v>0.3399802197267033</v>
       </c>
     </row>
     <row r="39">
@@ -1732,19 +1732,19 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(150.0, 500.0)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1754,11 +1754,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.3763373718726615</v>
+        <v>0.4534302887982024</v>
       </c>
     </row>
     <row r="40">
@@ -1766,19 +1766,19 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(150.0, 500.0)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1788,11 +1788,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.2556532040162887</v>
+        <v>0.3960892655081614</v>
       </c>
     </row>
     <row r="41">
@@ -1800,19 +1800,19 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(150.0, 500.0)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1822,11 +1822,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.3255760800573901</v>
+        <v>0.4283961894817646</v>
       </c>
     </row>
     <row r="42">
@@ -1834,19 +1834,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45226</v>
+        <v>45203</v>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_009_Unit 3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(100.0, 450.0)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1856,11 +1856,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.3564607086383018</v>
+        <v>0.6209182846145433</v>
       </c>
     </row>
     <row r="43">
@@ -1868,19 +1868,19 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45252</v>
+        <v>45203</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_009_Unit 3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(1900.0, 2050.0)</t>
+          <t>(100.0, 450.0)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1890,11 +1890,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.2560530988227461</v>
+        <v>0.8375245712063838</v>
       </c>
     </row>
     <row r="44">
@@ -1902,19 +1902,19 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45252</v>
+        <v>45203</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Channel.C_011</t>
+          <t>Channel.C_002_Unit 1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(1900.0, 2050.0)</t>
+          <t>(0.0, 500.0)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1924,11 +1924,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.3337301587301587</v>
+        <v>0.2604414230690678</v>
       </c>
     </row>
     <row r="45">
@@ -1936,19 +1936,19 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45274</v>
+        <v>45203</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Channel.C_024</t>
+          <t>Channel.C_004_Unit 2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(1400.0, 1550.0)</t>
+          <t>(0.0, 500.0)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1958,11 +1958,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.7528442004727506</v>
+        <v>0.6873532473375915</v>
       </c>
     </row>
     <row r="46">
@@ -1970,19 +1970,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45274</v>
+        <v>45203</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Channel.C_024</t>
+          <t>Channel.C_004_Unit 2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(1400.0, 1550.0)</t>
+          <t>(0.0, 500.0)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1992,11 +1992,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.7931144811437216</v>
+        <v>0.3388961089011431</v>
       </c>
     </row>
     <row r="47">
@@ -2004,19 +2004,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45274</v>
+        <v>45203</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Channel.C_026</t>
+          <t>Channel.C_004_Unit 2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(750.0, 850.0)</t>
+          <t>(0.0, 500.0)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2026,11 +2026,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.5641648986327205</v>
+        <v>0.2709994842489875</v>
       </c>
     </row>
     <row r="48">
@@ -2038,19 +2038,19 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45274</v>
+        <v>45203</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Channel.C_026</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(750.0, 850.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2060,11 +2060,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.4369195698130226</v>
+        <v>0.5139201626734957</v>
       </c>
     </row>
     <row r="49">
@@ -2072,19 +2072,19 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45274</v>
+        <v>45203</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Channel.C_026</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(750.0, 850.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2094,11 +2094,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.2627899626584673</v>
+        <v>0.4130900996349054</v>
       </c>
     </row>
     <row r="50">
@@ -2106,19 +2106,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45278</v>
+        <v>45203</v>
       </c>
       <c r="C50" t="n">
         <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Channel.C_029</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2128,11 +2128,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>69X</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.5662770485636313</v>
+        <v>0.5011791051364307</v>
       </c>
     </row>
     <row r="51">
@@ -2140,19 +2140,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45278</v>
+        <v>45203</v>
       </c>
       <c r="C51" t="n">
         <v>3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Channel.C_029</t>
+          <t>Channel.C_009_Unit 3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(50.0, 150.0)</t>
+          <t>(0.0, 700.0)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2162,11 +2162,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.6556493806189394</v>
+        <v>0.4979705701417866</v>
       </c>
     </row>
     <row r="52">
@@ -2174,19 +2174,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45195</v>
+        <v>45203</v>
       </c>
       <c r="C52" t="n">
         <v>3</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Channel.C_002_Unit 1</t>
+          <t>Channel.C_009_Unit 3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(0.0, 700.0)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2196,11 +2196,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.3491276898742337</v>
+        <v>0.2937962230178692</v>
       </c>
     </row>
     <row r="53">
@@ -2208,19 +2208,19 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45202</v>
+        <v>45203</v>
       </c>
       <c r="C53" t="n">
         <v>3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Channel.C_013_Unit 1</t>
+          <t>Channel.C_009_Unit 3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(200.0, 600.0)</t>
+          <t>(0.0, 700.0)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2230,11 +2230,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.2946290782193175</v>
+        <v>0.6592633600053226</v>
       </c>
     </row>
     <row r="54">
@@ -2242,19 +2242,19 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45202</v>
+        <v>45203</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Channel.C_013_Unit 1</t>
+          <t>Channel.C_021_Unit 2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(200.0, 600.0)</t>
+          <t>(150.0, 450.0)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.3890611754606188</v>
+        <v>0.3290104615328566</v>
       </c>
     </row>
     <row r="55">
@@ -2276,19 +2276,19 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45202</v>
+        <v>45203</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Channel.C_013_Unit 1</t>
+          <t>Channel.C_022_Unit 2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(200.0, 600.0)</t>
+          <t>(150.0, 650.0)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.7679440243156804</v>
+        <v>0.26515080261894</v>
       </c>
     </row>
     <row r="56">
@@ -2310,19 +2310,19 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45202</v>
+        <v>45203</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Channel.C_013_Unit 1</t>
+          <t>Channel.C_022_Unit 2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(200.0, 600.0)</t>
+          <t>(150.0, 650.0)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2332,11 +2332,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4791021024572061</v>
+        <v>0.5330497904310774</v>
       </c>
     </row>
     <row r="57">
@@ -2347,16 +2347,16 @@
         <v>45203</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Channel.C_004_Unit 1</t>
+          <t>Channel.C_022_Unit 2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
+          <t>(150.0, 650.0)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2366,11 +2366,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.3930257378820238</v>
+        <v>0.4115106576445308</v>
       </c>
     </row>
     <row r="58">
@@ -2381,16 +2381,16 @@
         <v>45203</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Channel.C_019_Unit 3</t>
+          <t>Channel.C_027_Unit 1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(100.0, 500.0)</t>
+          <t>(350.0, 650.0)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2400,11 +2400,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.3641188286886875</v>
+        <v>0.4888375099443119</v>
       </c>
     </row>
     <row r="59">
@@ -2415,16 +2415,16 @@
         <v>45203</v>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Channel.C_002_Unit 1</t>
+          <t>Channel.C_027_Unit 1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(0.0, 500.0)</t>
+          <t>(350.0, 650.0)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2434,11 +2434,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.2604414230690678</v>
+        <v>0.6536236986370267</v>
       </c>
     </row>
     <row r="60">
@@ -2449,16 +2449,16 @@
         <v>45203</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Channel.C_004_Unit 2</t>
+          <t>Channel.C_022_Unit 2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(0.0, 500.0)</t>
+          <t>(0.0, 750.0)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2468,11 +2468,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.6873532473375915</v>
+        <v>0.5465889859808275</v>
       </c>
     </row>
     <row r="61">
@@ -2483,16 +2483,16 @@
         <v>45203</v>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Channel.C_004_Unit 2</t>
+          <t>Channel.C_022_Unit 2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(0.0, 500.0)</t>
+          <t>(0.0, 750.0)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2502,11 +2502,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.3388961089011431</v>
+        <v>0.4266689330965995</v>
       </c>
     </row>
     <row r="62">
@@ -2517,16 +2517,16 @@
         <v>45203</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Channel.C_004_Unit 2</t>
+          <t>Channel.C_027_Unit 1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(0.0, 500.0)</t>
+          <t>(250.0, 750.0)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2536,11 +2536,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.2709994842489875</v>
+        <v>0.4991608610933161</v>
       </c>
     </row>
     <row r="63">
@@ -2551,16 +2551,16 @@
         <v>45203</v>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 1</t>
+          <t>Channel.C_027_Unit 1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(250.0, 750.0)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2570,11 +2570,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.5139201626734957</v>
+        <v>0.2611522452354493</v>
       </c>
     </row>
     <row r="64">
@@ -2585,16 +2585,16 @@
         <v>45203</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 1</t>
+          <t>Channel.C_027_Unit 1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(250.0, 750.0)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2604,11 +2604,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.4130900996349054</v>
+        <v>0.6424890905917263</v>
       </c>
     </row>
     <row r="65">
@@ -2616,19 +2616,19 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 1</t>
+          <t>Channel.C_004_Unit 1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(1000.0, 1100.0)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2638,11 +2638,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.5011791051364307</v>
+        <v>0.3902560086947965</v>
       </c>
     </row>
     <row r="66">
@@ -2650,19 +2650,19 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 3</t>
+          <t>Channel.C_004</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(0.0, 700.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2672,11 +2672,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.4979705701417866</v>
+        <v>0.6099903960471067</v>
       </c>
     </row>
     <row r="67">
@@ -2684,19 +2684,19 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 3</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(0.0, 700.0)</t>
+          <t>(500.0, 850.0)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2706,11 +2706,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.2937962230178692</v>
+        <v>0.4172529479839074</v>
       </c>
     </row>
     <row r="68">
@@ -2718,19 +2718,19 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Channel.C_009_Unit 3</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(0.0, 700.0)</t>
+          <t>(500.0, 850.0)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2740,11 +2740,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.6592633600053226</v>
+        <v>0.2644715627074705</v>
       </c>
     </row>
     <row r="69">
@@ -2752,19 +2752,19 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Channel.C_022_Unit 2</t>
+          <t>Channel.C_009_Unit 1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(500.0, 850.0)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2774,11 +2774,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>72X</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.5465889859808275</v>
+        <v>0.3097909400329603</v>
       </c>
     </row>
     <row r="70">
@@ -2786,19 +2786,19 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>45203</v>
+        <v>45208</v>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Channel.C_022_Unit 2</t>
+          <t>Channel.C_013</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(0.0, 750.0)</t>
+          <t>(600.0, 750.0)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2808,11 +2808,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.4266689330965995</v>
+        <v>0.4328725333148258</v>
       </c>
     </row>
     <row r="71">
@@ -2820,19 +2820,19 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>45203</v>
+        <v>45208</v>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_013</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(600.0, 750.0)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2842,11 +2842,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>151J</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.4991608610933161</v>
+        <v>0.5175608039695818</v>
       </c>
     </row>
     <row r="72">
@@ -2854,19 +2854,19 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_011</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(400.0, 600.0)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.2611522452354493</v>
+        <v>0.6703311882529281</v>
       </c>
     </row>
     <row r="73">
@@ -2888,19 +2888,19 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>45203</v>
+        <v>45209</v>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Channel.C_027_Unit 1</t>
+          <t>Channel.C_011</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(400.0, 600.0)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2910,11 +2910,11 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>87J</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.6424890905917263</v>
+        <v>0.2855258726554238</v>
       </c>
     </row>
     <row r="74">
@@ -2922,19 +2922,19 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>45204</v>
+        <v>45209</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Channel.C_004</t>
+          <t>Channel.C_011</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(0.0, 2000.0)</t>
+          <t>(400.0, 600.0)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2944,11 +2944,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.6099903960471067</v>
+        <v>0.3033038207935237</v>
       </c>
     </row>
     <row r="75">
@@ -2956,19 +2956,19 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>45210</v>
+        <v>45209</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(100.0, 500.0)</t>
+          <t>(300.0, 550.0)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.802032666616194</v>
+        <v>0.3947428074927921</v>
       </c>
     </row>
     <row r="76">
@@ -2990,19 +2990,19 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>45210</v>
+        <v>45209</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(100.0, 500.0)</t>
+          <t>(300.0, 550.0)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.2647701414337452</v>
+        <v>0.6388738325672818</v>
       </c>
     </row>
     <row r="77">
@@ -3024,19 +3024,19 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>45223</v>
+        <v>45209</v>
       </c>
       <c r="C77" t="n">
         <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(300.0, 550.0)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3046,11 +3046,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>94B</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.6701726646540971</v>
+        <v>0.3964509637803838</v>
       </c>
     </row>
     <row r="78">
@@ -3058,19 +3058,19 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>45223</v>
+        <v>45209</v>
       </c>
       <c r="C78" t="n">
         <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Channel.C_002</t>
+          <t>Channel.C_021</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(250.0, 750.0)</t>
+          <t>(1550.0, 1650.0)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3080,11 +3080,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.3545068274119657</v>
+        <v>0.2569610588578257</v>
       </c>
     </row>
     <row r="79">
@@ -3092,19 +3092,19 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>45230</v>
+        <v>45210</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Channel.C_005</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(250.0, 600.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.4027017714009808</v>
+        <v>0.3847344105749465</v>
       </c>
     </row>
     <row r="80">
@@ -3126,19 +3126,19 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>45230</v>
+        <v>45210</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Channel.C_005</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(250.0, 600.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3148,11 +3148,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.3286482611158116</v>
+        <v>0.872866297837493</v>
       </c>
     </row>
     <row r="81">
@@ -3160,19 +3160,19 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>45230</v>
+        <v>45210</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Channel.C_005</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(250.0, 600.0)</t>
+          <t>(150.0, 400.0)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3182,11 +3182,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.2573441995421676</v>
+        <v>0.3040417237275248</v>
       </c>
     </row>
     <row r="82">
@@ -3194,19 +3194,19 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>45230</v>
+        <v>45210</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Channel.C_005</t>
+          <t>Channel.C_010</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(250.0, 600.0)</t>
+          <t>(2000.0, 2200.0)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3216,11 +3216,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>72X</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.8079259290504914</v>
+        <v>0.4136485556832592</v>
       </c>
     </row>
     <row r="83">
@@ -3228,19 +3228,19 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>45230</v>
+        <v>45210</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_010</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(100.0, 600.0)</t>
+          <t>(2000.0, 2200.0)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3250,11 +3250,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.626784783891951</v>
+        <v>0.6303295039415495</v>
       </c>
     </row>
     <row r="84">
@@ -3262,19 +3262,19 @@
         <v>82</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>45230</v>
+        <v>45210</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_010</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(100.0, 600.0)</t>
+          <t>(2000.0, 2200.0)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>87J</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.5055802008426702</v>
+        <v>0.8015063835179573</v>
       </c>
     </row>
     <row r="85">
@@ -3296,19 +3296,19 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45230</v>
+        <v>45210</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(100.0, 600.0)</t>
+          <t>(100.0, 500.0)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3318,11 +3318,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.404561651525172</v>
+        <v>0.802032666616194</v>
       </c>
     </row>
     <row r="86">
@@ -3330,19 +3330,19 @@
         <v>84</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>45230</v>
+        <v>45210</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Channel.C_020</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(100.0, 600.0)</t>
+          <t>(100.0, 500.0)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3352,11 +3352,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>151J</t>
+          <t>67G</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.8099220408833812</v>
+        <v>0.2647701414337452</v>
       </c>
     </row>
     <row r="87">
@@ -3364,19 +3364,19 @@
         <v>85</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>45238</v>
+        <v>45210</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Channel.C_007</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3386,11 +3386,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>94B</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.3260780638045776</v>
+        <v>0.759144027018426</v>
       </c>
     </row>
     <row r="88">
@@ -3398,19 +3398,19 @@
         <v>86</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>45238</v>
+        <v>45210</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Channel.C_007</t>
+          <t>Channel.C_002</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
+          <t>(0.0, 2000.0)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3420,11 +3420,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>110E</t>
+          <t>143H</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.8351764021321147</v>
+        <v>0.2619753014117013</v>
       </c>
     </row>
     <row r="89">
@@ -3432,10 +3432,10 @@
         <v>87</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>45238</v>
+        <v>45226</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
+          <t>(1750.0, 1900.0)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3454,11 +3454,11 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>67G</t>
+          <t>110E</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.2524659318518986</v>
+        <v>0.7340611791706362</v>
       </c>
     </row>
     <row r="90">
@@ -3466,19 +3466,19 @@
         <v>88</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>45238</v>
+        <v>45226</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Channel.C_007</t>
+          <t>Channel.C_011</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>(100.0, 700.0)</t>
+          <t>(200.0, 700.0)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3488,11 +3488,11 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>143H</t>
+          <t>69X</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.2844966303385066</v>
+        <v>0.3598587278629846</v>
       </c>
     </row>
     <row r="91">
@@ -3500,32 +3500,1562 @@
         <v>89</v>
       </c>
       <c r="B91" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>(200.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0.386955649485476</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C92" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>(200.0, 650.0)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0.4169555837918038</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C93" t="n">
+        <v>4</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>(200.0, 650.0)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0.3291609580515368</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C94" t="n">
+        <v>4</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0.3763373718726615</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C95" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Channel.C_011</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0.2556532040162887</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0.3255760800573901</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="C97" t="n">
+        <v>4</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>(0.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0.3564607086383018</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Channel.C_013</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>(850.0, 950.0)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0.3241405921941143</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Channel.C_013</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>(850.0, 950.0)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0.8604624492896974</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="C100" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Channel.C_006</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>(2200.0, 2300.0)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0.6569787889213438</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>45255</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Channel.C_019</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>(100.0, 500.0)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0.294047784775227</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>45255</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Channel.C_019</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>(100.0, 500.0)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0.4567005947369087</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>45255</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Channel.C_018</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>(50.0, 150.0)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0.4463585237182068</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>45255</v>
+      </c>
+      <c r="C104" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Channel.C_018</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>(50.0, 150.0)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>110E</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0.2576935046414158</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C105" t="n">
+        <v>3</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>(700.0, 850.0)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0.3387466372294177</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>(700.0, 850.0)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0.3381179740310429</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C107" t="n">
+        <v>4</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Channel.C_015</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>(350.0, 500.0)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>110E</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0.3293437729129568</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C108" t="n">
+        <v>4</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Channel.C_015</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>(350.0, 500.0)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0.3947323185056439</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C109" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Channel.C_015</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>(650.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0.2945073215467162</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C110" t="n">
+        <v>4</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Channel.C_015</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>(650.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0.7942085337153382</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Channel.C_024</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>(1450.0, 1750.0)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>69X</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>0.6991508956699787</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Channel.C_024</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>(1450.0, 1750.0)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0.5830687683863051</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Channel.C_006</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>(1900.0, 2000.0)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0.7292552851969234</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C114" t="n">
+        <v>4</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Channel.C_006</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>(1900.0, 2000.0)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0.3687372734155074</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C115" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Channel.C_008</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>(750.0, 850.0)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>0.6226249184436214</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="C116" t="n">
+        <v>4</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Channel.C_008</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>(750.0, 850.0)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0.7821261047746013</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C117" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Channel.C_012_Unit 2</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>(200.0, 350.0)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>72X</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0.322913482115561</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Channel.C_012_Unit 2</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>(200.0, 350.0)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0.3208441258558722</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C119" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Channel.C_012_Unit 2</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>(200.0, 350.0)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0.744855176059299</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>45278</v>
+      </c>
+      <c r="C120" t="n">
+        <v>3</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Channel.C_020_Unit 1</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>(150.0, 400.0)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>87J</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0.6984003589636587</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Channel.C_027_Unit 1</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>(0.0, 300.0)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>94B</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0.5092734647876507</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>45223</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Channel.C_002</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>(250.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>94B</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>0.6701726646540971</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>45223</v>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Channel.C_002</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>(250.0, 750.0)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3545068274119657</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Channel.C_005</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>(250.0, 600.0)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>0.4027017714009808</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Channel.C_005</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>(250.0, 600.0)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3286482611158116</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Channel.C_005</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>(250.0, 600.0)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>0.2573441995421676</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Channel.C_005</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>(250.0, 600.0)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>0.8079259290504914</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>(100.0, 600.0)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>0.626784783891951</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>(100.0, 600.0)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>110E</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>0.5055802008426702</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>(100.0, 600.0)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>0.404561651525172</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Channel.C_020</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>(100.0, 600.0)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>151J</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>0.8099220408833812</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="2" t="n">
         <v>45238</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C132" t="n">
         <v>1</v>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>Channel.C_007</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>(100.0, 700.0)</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>AffliationTo</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3260780638045776</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>45238</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>(100.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>110E</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>0.8351764021321147</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>45238</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>(100.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>67G</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>0.2524659318518986</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>45238</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>(100.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>143H</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>0.2844966303385066</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>45238</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Channel.C_007</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>(100.0, 700.0)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>AffliationTo</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
         <is>
           <t>151J</t>
         </is>
       </c>
-      <c r="H91" t="n">
+      <c r="H136" t="n">
         <v>0.2581404434048395</v>
       </c>
     </row>
